--- a/data/trans_orig/Q64D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar</t>
+          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar (tasa de respuesta: 88,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,91</t>
+          <t>4,94; 10,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 25,84</t>
+          <t>10,68; 25,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 18,55</t>
+          <t>8,59; 17,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,6</t>
+          <t>2,31; 8,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,0</t>
+          <t>2,8; 7,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,1</t>
+          <t>3,61; 10,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,78</t>
+          <t>4,87; 13,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,8</t>
+          <t>2,91; 8,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,56</t>
+          <t>4,34; 8,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 17,65</t>
+          <t>8,6; 17,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,28</t>
+          <t>7,79; 14,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,83</t>
+          <t>3,16; 7,15</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 14,44</t>
+          <t>8,34; 14,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 18,34</t>
+          <t>8,66; 17,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,68</t>
+          <t>4,58; 7,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,38</t>
+          <t>4,75; 11,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 16,09</t>
+          <t>7,72; 16,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 17,21</t>
+          <t>7,79; 17,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,0</t>
+          <t>3,87; 9,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 19,21</t>
+          <t>5,83; 19,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,85</t>
+          <t>8,87; 14,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 15,8</t>
+          <t>9,07; 15,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,56</t>
+          <t>4,54; 7,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,6</t>
+          <t>5,74; 11,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,28</t>
+          <t>4,08; 9,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,14</t>
+          <t>2,42; 6,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,46</t>
+          <t>4,6; 11,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 11,36</t>
+          <t>4,11; 11,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 10,79</t>
+          <t>3,32; 10,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,72</t>
+          <t>3,79; 10,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,97</t>
+          <t>5,37; 18,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 14,9</t>
+          <t>7,72; 14,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,66</t>
+          <t>4,3; 8,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,53</t>
+          <t>3,23; 6,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,44</t>
+          <t>5,6; 12,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,03</t>
+          <t>6,72; 11,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,03</t>
+          <t>5,17; 12,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 15,92</t>
+          <t>6,76; 15,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 33,2</t>
+          <t>14,61; 34,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 14,01</t>
+          <t>4,64; 13,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,46</t>
+          <t>4,95; 11,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,41</t>
+          <t>4,31; 11,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 19,63</t>
+          <t>7,39; 20,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 14,22</t>
+          <t>2,97; 13,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,76</t>
+          <t>5,81; 10,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,85</t>
+          <t>6,37; 12,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,24; 23,67</t>
+          <t>12,62; 24,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,18</t>
+          <t>4,37; 12,09</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,08</t>
+          <t>5,41; 12,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,06</t>
+          <t>4,11; 12,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,47</t>
+          <t>3,21; 10,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,11; 56,83</t>
+          <t>37,16; 55,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 29,58</t>
+          <t>13,27; 29,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 22,48</t>
+          <t>5,8; 22,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,26</t>
+          <t>3,44; 14,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,77; 63,28</t>
+          <t>46,1; 63,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 16,13</t>
+          <t>8,65; 16,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 14,23</t>
+          <t>5,8; 13,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,12</t>
+          <t>3,91; 10,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,09; 57,01</t>
+          <t>43,41; 57,18</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 29,69</t>
+          <t>4,83; 27,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,37</t>
+          <t>4,05; 10,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 24,32</t>
+          <t>4,0; 24,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 14,69</t>
+          <t>5,14; 14,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,72</t>
+          <t>3,22; 8,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 22,97</t>
+          <t>4,31; 21,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 29,15</t>
+          <t>5,57; 25,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 19,73</t>
+          <t>5,46; 19,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 21,16</t>
+          <t>4,86; 19,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,56</t>
+          <t>5,02; 12,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 18,85</t>
+          <t>5,62; 19,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,42</t>
+          <t>6,37; 13,88</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,02</t>
+          <t>6,61; 11,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,48</t>
+          <t>5,32; 11,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 15,51</t>
+          <t>8,93; 15,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,16; 36,22</t>
+          <t>22,87; 35,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,64</t>
+          <t>5,63; 11,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,93</t>
+          <t>4,98; 10,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,8</t>
+          <t>10,05; 16,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,75; 22,96</t>
+          <t>15,75; 22,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,76</t>
+          <t>6,61; 10,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,01</t>
+          <t>5,84; 9,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,22</t>
+          <t>10,08; 14,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,73; 28,08</t>
+          <t>20,69; 28,1</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,0</t>
+          <t>10,72; 17,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,15</t>
+          <t>6,14; 10,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,64</t>
+          <t>6,44; 11,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 30,6</t>
+          <t>6,04; 30,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,7</t>
+          <t>6,89; 12,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,74</t>
+          <t>6,83; 11,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,91; 15,24</t>
+          <t>7,76; 14,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,72; 33,1</t>
+          <t>20,66; 33,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,65</t>
+          <t>10,08; 14,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,02</t>
+          <t>7,01; 10,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,95</t>
+          <t>7,98; 12,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 28,86</t>
+          <t>6,76; 28,81</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,53</t>
+          <t>8,67; 11,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,43</t>
+          <t>7,7; 10,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,4</t>
+          <t>8,67; 11,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,74; 19,33</t>
+          <t>9,41; 19,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,9</t>
+          <t>7,29; 9,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,98</t>
+          <t>7,23; 9,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,15</t>
+          <t>8,88; 11,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,08; 17,92</t>
+          <t>12,93; 17,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,64</t>
+          <t>8,46; 10,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 9,69</t>
+          <t>7,85; 9,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,23; 11,32</t>
+          <t>9,08; 11,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,73; 17,89</t>
+          <t>11,62; 17,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,49</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,1</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,9</t>
+          <t>4,87; 11,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 25,82</t>
+          <t>10,44; 25,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 17,84</t>
+          <t>8,41; 18,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,06</t>
+          <t>2,17; 6,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,85</t>
+          <t>2,67; 8,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,89</t>
+          <t>3,88; 11,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,67</t>
+          <t>5,16; 14,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,52</t>
+          <t>3,0; 7,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,59</t>
+          <t>4,55; 8,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 17,9</t>
+          <t>8,75; 18,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 14,67</t>
+          <t>7,65; 14,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,15</t>
+          <t>2,9; 6,01</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>8,11</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 14,72</t>
+          <t>8,37; 14,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,48</t>
+          <t>8,61; 17,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,48</t>
+          <t>4,48; 7,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,52</t>
+          <t>4,45; 10,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,1</t>
+          <t>7,71; 16,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 17,29</t>
+          <t>7,79; 17,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,36</t>
+          <t>3,73; 9,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 19,03</t>
+          <t>6,11; 16,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,32</t>
+          <t>8,77; 13,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,54</t>
+          <t>9,05; 15,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,29</t>
+          <t>4,58; 7,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 11,68</t>
+          <t>5,92; 11,63</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,68</t>
+          <t>4,09; 9,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,01</t>
+          <t>2,46; 6,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,46</t>
+          <t>4,83; 11,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,12</t>
+          <t>4,16; 11,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,66</t>
+          <t>3,54; 10,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,28</t>
+          <t>3,65; 9,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 18,71</t>
+          <t>5,33; 18,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,9</t>
+          <t>8,0; 15,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,76</t>
+          <t>4,37; 8,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,4</t>
+          <t>3,32; 6,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 12,19</t>
+          <t>5,87; 12,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,3</t>
+          <t>6,57; 11,48</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>9,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,07</t>
+          <t>5,29; 12,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,55</t>
+          <t>6,69; 15,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 34,84</t>
+          <t>14,74; 33,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 13,76</t>
+          <t>4,49; 12,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,54</t>
+          <t>5,08; 11,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,87</t>
+          <t>4,19; 11,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 20,25</t>
+          <t>7,68; 18,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 13,8</t>
+          <t>7,79; 19,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,49</t>
+          <t>5,84; 10,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,28</t>
+          <t>6,27; 11,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 24,23</t>
+          <t>12,88; 24,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,09</t>
+          <t>7,15; 14,35</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,24</t>
+          <t>45,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,6</t>
+          <t>53,46</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,96</t>
+          <t>49,13</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,73</t>
+          <t>5,58; 12,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,72</t>
+          <t>4,27; 12,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,85</t>
+          <t>3,12; 10,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,16; 55,96</t>
+          <t>37,02; 55,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,27; 29,36</t>
+          <t>13,62; 29,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 22,32</t>
+          <t>6,07; 21,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 14,82</t>
+          <t>3,41; 14,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,1; 63,6</t>
+          <t>44,22; 62,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 16,09</t>
+          <t>9,24; 16,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,96</t>
+          <t>6,02; 14,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,33</t>
+          <t>4,04; 10,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,41; 57,18</t>
+          <t>43,29; 56,14</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>8,99</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 27,03</t>
+          <t>4,7; 32,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,99</t>
+          <t>3,94; 10,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 24,24</t>
+          <t>3,87; 23,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 14,48</t>
+          <t>5,0; 14,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,88</t>
+          <t>3,28; 9,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 21,75</t>
+          <t>4,29; 23,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 25,17</t>
+          <t>5,54; 27,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,54</t>
+          <t>5,46; 20,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 19,86</t>
+          <t>4,79; 19,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,17</t>
+          <t>4,76; 13,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 19,49</t>
+          <t>5,58; 19,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,88</t>
+          <t>6,12; 13,47</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,75</t>
+          <t>26,87</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,07</t>
+          <t>19,71</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,04</t>
+          <t>23,33</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,9</t>
+          <t>6,44; 11,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,55</t>
+          <t>4,9; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 15,4</t>
+          <t>8,9; 15,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,87; 35,86</t>
+          <t>21,72; 33,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,67</t>
+          <t>5,61; 12,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,67</t>
+          <t>4,99; 10,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,01</t>
+          <t>10,22; 16,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,75; 22,86</t>
+          <t>16,68; 24,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,76</t>
+          <t>6,79; 10,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,95</t>
+          <t>5,78; 9,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,29</t>
+          <t>10,04; 14,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,69; 28,1</t>
+          <t>19,98; 26,93</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,82</t>
+          <t>29,41</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25,01</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,23</t>
+          <t>26,96</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,72; 17,05</t>
+          <t>10,8; 17,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,56</t>
+          <t>6,11; 10,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,93</t>
+          <t>6,51; 11,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 30,9</t>
+          <t>25,75; 32,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,77</t>
+          <t>6,65; 12,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,85</t>
+          <t>6,73; 11,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,76; 14,78</t>
+          <t>7,7; 14,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 33,37</t>
+          <t>19,18; 27,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,93</t>
+          <t>10,0; 14,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,21</t>
+          <t>6,79; 9,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,12</t>
+          <t>7,84; 12,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 28,81</t>
+          <t>24,22; 29,75</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,69</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15,72</t>
+          <t>16,76</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,53</t>
+          <t>8,81; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,39</t>
+          <t>7,66; 10,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,72</t>
+          <t>8,71; 11,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 19,21</t>
+          <t>16,56; 20,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,89</t>
+          <t>7,32; 9,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 9,88</t>
+          <t>7,17; 10,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,95</t>
+          <t>8,88; 12,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,98</t>
+          <t>15,24; 18,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,52</t>
+          <t>8,59; 10,51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,85; 9,75</t>
+          <t>7,86; 9,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,26</t>
+          <t>9,01; 11,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,87</t>
+          <t>16,39; 18,98</t>
         </is>
       </c>
     </row>
